--- a/artfynd/A 2457-2022 artfynd.xlsx
+++ b/artfynd/A 2457-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 2457-2022 artfynd.xlsx
+++ b/artfynd/A 2457-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>100201606</v>
+        <v>78739783</v>
       </c>
       <c r="B2" t="n">
-        <v>95198</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,36 +686,49 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2606</v>
+        <v>1339</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Svenljunga, Vg</t>
+          <t>Mjöbäcks skolskog, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>371976.4536340896</v>
+        <v>372099</v>
       </c>
       <c r="R2" t="n">
-        <v>6353653.45835344</v>
+        <v>6353597</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -747,22 +755,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-04-24</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-07-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-04-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-07-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,33 +769,59 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>brant slänt med stora grova granar och flera lövträdsarter, en del granlågor</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>vanlig gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Gammal granlåga förrötad av klibbticka</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies # Gammal granlåga förrötad av klibbticka</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Mariann Andersson Norrman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Mariann Andersson Norrman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>61943318</v>
+        <v>90838142</v>
       </c>
       <c r="B3" t="n">
-        <v>83136</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,37 +829,48 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3518</v>
+        <v>1339</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Mjöbäcks skolskog, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>372016.1164801507</v>
+        <v>372003</v>
       </c>
       <c r="R3" t="n">
-        <v>6353674.920922825</v>
+        <v>6353585</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -859,22 +894,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2016-10-16</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2016-10-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,83 +908,76 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Elin Götmark</t>
+          <t>Mariann Andersson Norrman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Elin Götmark</t>
+          <t>Mariann Andersson Norrman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>78587033</v>
+        <v>100201606</v>
       </c>
       <c r="B4" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97785</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2606</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Dumort.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mjöbäck kyrka, Vg, Vg</t>
+          <t>Svenljunga, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>372034.1794898407</v>
+        <v>371976</v>
       </c>
       <c r="R4" t="n">
-        <v>6353611.658506621</v>
+        <v>6353653</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -986,22 +1004,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2019-06-23</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2019-06-23</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,36 +1020,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Mariann Andersson Norrman</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mariann Andersson Norrman</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>78739783</v>
+        <v>100199305</v>
       </c>
       <c r="B5" t="n">
-        <v>90005</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1049,49 +1047,36 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1339</v>
+        <v>2810</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mjöbäcks skolskog, Vg</t>
+          <t>Svenljunga, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>372099.2414791787</v>
+        <v>372072</v>
       </c>
       <c r="R5" t="n">
-        <v>6353596.655820108</v>
+        <v>6353667</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1118,22 +1103,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2019-07-01</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2019-07-01</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,64 +1117,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>brant slänt med stora grova granar och flera lövträdsarter, en del granlågor</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>vanlig gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies subsp. abies</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>Gammal granlåga förrötad av klibbticka</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies subsp. abies # Gammal granlåga förrötad av klibbticka</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Mariann Andersson Norrman</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mariann Andersson Norrman</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>100199305</v>
+        <v>61943318</v>
       </c>
       <c r="B6" t="n">
-        <v>93054</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>85274</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1207,39 +1146,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2810</v>
+        <v>3518</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Svenljunga, Vg</t>
+          <t>Mjöbäcks skolskog, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>372072.2156833368</v>
+        <v>372016</v>
       </c>
       <c r="R6" t="n">
-        <v>6353667.764813268</v>
+        <v>6353675</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1263,22 +1200,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-04-24</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-10-16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-04-24</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-10-16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1293,15 +1220,374 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Elin Götmark</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Elin Götmark</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>71517757</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57966</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Mjöbäcks skolskog, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>372003</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6353585</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Svenljunga</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Mjöbäck</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2018-04-28</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2018-04-28</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mariann Andersson Norrman</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mariann Andersson Norrman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>71517819</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Mjöbäcks skolskog, Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>372003</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6353585</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Svenljunga</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Mjöbäck</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2018-04-30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2018-04-30</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Gammal Granskog med inslag av lövträd och ett flertal döda träd och lågor</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mariann Andersson Norrman</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mariann Andersson Norrman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>78587033</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Mjöbäck kyrka, Vg, Vg</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>372034</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6353612</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Svenljunga</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Mjöbäck</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2019-06-23</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2019-06-23</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Mariann Andersson Norrman</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Mariann Andersson Norrman</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2457-2022 artfynd.xlsx
+++ b/artfynd/A 2457-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -815,6 +820,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78739783</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -934,6 +944,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90838142</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1033,6 +1048,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100201606</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1132,6 +1152,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100199305</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1229,6 +1254,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61943318</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1345,6 +1375,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71517757</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1471,6 +1506,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71517819</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1588,8 +1628,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78587033</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>